--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_44.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2920135.254436548</v>
+        <v>2913094.603846669</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979915</v>
+        <v>9947345.838828402</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979915</v>
+        <v>9947345.838828402</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14285552.91847333</v>
+        <v>14285642.16566955</v>
       </c>
     </row>
   </sheetData>
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>263.2631591877375</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -739,22 +739,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>26.73873623149473</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>167.1158402638074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -909,10 +909,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>26.34349040625725</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -979,16 +979,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1024,13 +1024,13 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>180.775050041147</v>
       </c>
       <c r="U6" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>140.0682043885218</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>250.414304340989</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>168.4149913854146</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>94.84816780232291</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110.3965447195857</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1261,10 +1261,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>284.85671905313</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>73.04152018756581</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1507,13 +1507,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X12" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1608,7 +1608,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D14" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E14" t="n">
         <v>54.36328960686865</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1687,13 +1687,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>73.04152018756581</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>64.74007562773993</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>288.3734759809475</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>121.4947832967418</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1978,13 +1978,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V18" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W18" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X18" t="n">
-        <v>69.86273944538755</v>
+        <v>132.5405019708301</v>
       </c>
       <c r="Y18" t="n">
         <v>49.39139276613435</v>
@@ -2094,7 +2094,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>58.00965870352741</v>
+        <v>65.85585008894192</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2133,7 +2133,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U20" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V20" t="n">
         <v>279.8510241668239</v>
@@ -2161,7 +2161,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2173,10 +2173,10 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>195.5513766340942</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2221,7 +2221,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>49.39139276613435</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T23" t="n">
         <v>236.6755817285639</v>
@@ -2382,7 +2382,7 @@
         <v>242.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>161.3174326828064</v>
+        <v>169.1636240682209</v>
       </c>
     </row>
     <row r="24">
@@ -2401,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>80.50967533902158</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>144.8481678023229</v>
+        <v>152.6943591877374</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>62.67776252544251</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>197.2737972923793</v>
@@ -2686,10 +2686,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U27" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V27" t="n">
-        <v>414.5106671915202</v>
+        <v>127.1884297169628</v>
       </c>
       <c r="W27" t="n">
         <v>82.37314290982852</v>
@@ -2802,7 +2802,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
         <v>58.00965870352741</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>7.846191385414608</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2881,13 +2881,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T30" t="n">
-        <v>55.35776521751382</v>
+        <v>142.295991867929</v>
       </c>
       <c r="U30" t="n">
         <v>50.21035976018675</v>
@@ -2935,7 +2935,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>244.9427694002283</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -3039,13 +3039,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3151,13 +3151,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>259.9515598178217</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S33" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900539</v>
       </c>
       <c r="T33" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U33" t="n">
         <v>50.21035976018675</v>
@@ -3276,13 +3276,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>61.60356367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3358,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>80.50967533902144</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915769</v>
       </c>
     </row>
     <row r="37">
@@ -3501,7 +3501,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D38" t="n">
         <v>60.33915573984979</v>
@@ -3555,7 +3555,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U38" t="n">
-        <v>299.2212965486107</v>
+        <v>307.0674879340252</v>
       </c>
       <c r="V38" t="n">
         <v>279.8510241668239</v>
@@ -3589,13 +3589,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.2737972923793</v>
+        <v>277.7834726314009</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3868,7 +3868,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429564</v>
       </c>
       <c r="U42" t="n">
         <v>400.2103597601867</v>
@@ -3880,7 +3880,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>7.846191385414503</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>144.8481678023229</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4111,16 +4111,16 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>127.1884297169627</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>112.069155291577</v>
       </c>
     </row>
     <row r="46">
@@ -4330,7 +4330,7 @@
         <v>33.68</v>
       </c>
       <c r="M2" t="n">
-        <v>450.47</v>
+        <v>33.68</v>
       </c>
       <c r="N2" t="n">
         <v>450.47</v>
@@ -4345,7 +4345,7 @@
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S2" t="n">
         <v>1418.077616982083</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>731.265640524864</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="C3" t="n">
-        <v>731.265640524864</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="D3" t="n">
-        <v>379.8134315372855</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="E3" t="n">
-        <v>33.68</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="F3" t="n">
-        <v>33.68</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="G3" t="n">
-        <v>33.68</v>
+        <v>396.2121448665817</v>
       </c>
       <c r="H3" t="n">
-        <v>33.68</v>
+        <v>60.68882447625731</v>
       </c>
       <c r="I3" t="n">
         <v>33.68</v>
@@ -4421,31 +4421,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>973.1146453614743</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T3" t="n">
-        <v>967.7027613033796</v>
+        <v>792.8752208079458</v>
       </c>
       <c r="U3" t="n">
-        <v>967.4902766971303</v>
+        <v>792.6627362016965</v>
       </c>
       <c r="V3" t="n">
-        <v>952.8330371097362</v>
+        <v>778.0054966143024</v>
       </c>
       <c r="W3" t="n">
-        <v>920.1328927563741</v>
+        <v>745.3053522609403</v>
       </c>
       <c r="X3" t="n">
-        <v>900.0695195792149</v>
+        <v>725.2419790837811</v>
       </c>
       <c r="Y3" t="n">
-        <v>731.265640524864</v>
+        <v>725.2419790837811</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>818.159055707231</v>
+        <v>383.5321839101395</v>
       </c>
       <c r="C4" t="n">
-        <v>944.1610615256668</v>
+        <v>509.5341897285753</v>
       </c>
       <c r="D4" t="n">
-        <v>1057.480205650667</v>
+        <v>509.5341897285753</v>
       </c>
       <c r="E4" t="n">
-        <v>1057.480205650667</v>
+        <v>625.7549448492859</v>
       </c>
       <c r="F4" t="n">
-        <v>1057.480205650667</v>
+        <v>750.1159174412214</v>
       </c>
       <c r="G4" t="n">
-        <v>1057.480205650667</v>
+        <v>903.5224833281067</v>
       </c>
       <c r="H4" t="n">
-        <v>1226.996790810065</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="I4" t="n">
-        <v>1226.996790810065</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4509,22 +4509,22 @@
         <v>33.68</v>
       </c>
       <c r="T4" t="n">
-        <v>221.7556791588049</v>
+        <v>33.68</v>
       </c>
       <c r="U4" t="n">
-        <v>468.3068717970915</v>
+        <v>33.68</v>
       </c>
       <c r="V4" t="n">
-        <v>667.1282646830375</v>
+        <v>232.501392885946</v>
       </c>
       <c r="W4" t="n">
-        <v>667.1282646830375</v>
+        <v>232.501392885946</v>
       </c>
       <c r="X4" t="n">
-        <v>818.159055707231</v>
+        <v>383.5321839101395</v>
       </c>
       <c r="Y4" t="n">
-        <v>818.159055707231</v>
+        <v>383.5321839101395</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.3301851396645</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>65.35586368209485</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D5" t="n">
-        <v>54.91227202568093</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E5" t="n">
-        <v>50.50490878641967</v>
+        <v>220.6210617009798</v>
       </c>
       <c r="F5" t="n">
-        <v>45.565889889438</v>
+        <v>215.6820428039981</v>
       </c>
       <c r="G5" t="n">
-        <v>41.77056434699738</v>
+        <v>211.8867172615575</v>
       </c>
       <c r="H5" t="n">
-        <v>33.68</v>
+        <v>185.2771309926108</v>
       </c>
       <c r="I5" t="n">
         <v>33.68</v>
@@ -4582,28 +4582,28 @@
         <v>1684</v>
       </c>
       <c r="R5" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S5" t="n">
-        <v>1418.077616982083</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1229.516423316867</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>977.7777399344324</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>310.5996251784331</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>369.2033203903244</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="C6" t="n">
-        <v>369.2033203903244</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="D6" t="n">
-        <v>369.2033203903244</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="E6" t="n">
-        <v>369.2033203903244</v>
+        <v>376.7469114524009</v>
       </c>
       <c r="F6" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="G6" t="n">
-        <v>369.2033203903244</v>
+        <v>33.68</v>
       </c>
       <c r="H6" t="n">
         <v>33.68</v>
@@ -4667,22 +4667,22 @@
         <v>973.1146453614743</v>
       </c>
       <c r="T6" t="n">
-        <v>967.7027613033796</v>
+        <v>790.5135847138511</v>
       </c>
       <c r="U6" t="n">
-        <v>563.4498726567263</v>
+        <v>790.3011001076018</v>
       </c>
       <c r="V6" t="n">
-        <v>421.9668379208456</v>
+        <v>775.6438605202077</v>
       </c>
       <c r="W6" t="n">
-        <v>389.2666935674835</v>
+        <v>742.9437161668455</v>
       </c>
       <c r="X6" t="n">
-        <v>369.2033203903244</v>
+        <v>722.8803429896864</v>
       </c>
       <c r="Y6" t="n">
-        <v>369.2033203903244</v>
+        <v>722.8803429896864</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>754.0496039388236</v>
+        <v>1250.466867406406</v>
       </c>
       <c r="C7" t="n">
-        <v>880.0516097572594</v>
+        <v>1376.468873224842</v>
       </c>
       <c r="D7" t="n">
-        <v>993.3707538822595</v>
+        <v>1489.788017349842</v>
       </c>
       <c r="E7" t="n">
-        <v>1111.199658093672</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="F7" t="n">
-        <v>1111.199658093672</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="G7" t="n">
-        <v>1264.606223980558</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="H7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="I7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="J7" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K7" t="n">
         <v>1544.487243076824</v>
@@ -4746,22 +4746,22 @@
         <v>70.93025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>70.93025509417312</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>317.4814477324597</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>516.3028406184058</v>
+        <v>704.3785197772106</v>
       </c>
       <c r="W7" t="n">
-        <v>642.2922662725314</v>
+        <v>876.269438036888</v>
       </c>
       <c r="X7" t="n">
-        <v>642.2922662725314</v>
+        <v>1027.300229061082</v>
       </c>
       <c r="Y7" t="n">
-        <v>642.2922662725314</v>
+        <v>1138.709529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4795,19 +4795,19 @@
         <v>33.68</v>
       </c>
       <c r="J8" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="K8" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="L8" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="M8" t="n">
-        <v>841.7791130376559</v>
+        <v>450.47</v>
       </c>
       <c r="N8" t="n">
-        <v>1258.569113037656</v>
+        <v>867.26</v>
       </c>
       <c r="O8" t="n">
         <v>1267.21</v>
@@ -4819,28 +4819,28 @@
         <v>1684</v>
       </c>
       <c r="R8" t="n">
-        <v>1513.88384708544</v>
+        <v>1684</v>
       </c>
       <c r="S8" t="n">
-        <v>1418.077616982083</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>1229.516423316867</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U8" t="n">
-        <v>977.7777399344324</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>745.6049882507718</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W8" t="n">
-        <v>504.8236993811278</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X8" t="n">
-        <v>310.5996251784331</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>385.1322089875785</v>
+        <v>33.68</v>
       </c>
       <c r="C9" t="n">
-        <v>385.1322089875785</v>
+        <v>33.68</v>
       </c>
       <c r="D9" t="n">
         <v>33.68</v>
@@ -4895,31 +4895,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S9" t="n">
-        <v>973.1146453614743</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T9" t="n">
-        <v>967.7027613033796</v>
+        <v>388.8348167675417</v>
       </c>
       <c r="U9" t="n">
-        <v>967.4902766971303</v>
+        <v>101.1007571179154</v>
       </c>
       <c r="V9" t="n">
-        <v>952.8330371097362</v>
+        <v>86.44351753052129</v>
       </c>
       <c r="W9" t="n">
-        <v>920.1328927563741</v>
+        <v>53.74337317715914</v>
       </c>
       <c r="X9" t="n">
-        <v>900.0695195792149</v>
+        <v>33.68</v>
       </c>
       <c r="Y9" t="n">
-        <v>496.6438703204933</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>783.0951972337734</v>
+        <v>1250.466867406406</v>
       </c>
       <c r="C10" t="n">
-        <v>909.0972030522092</v>
+        <v>1376.468873224842</v>
       </c>
       <c r="D10" t="n">
-        <v>1022.416347177209</v>
+        <v>1489.788017349842</v>
       </c>
       <c r="E10" t="n">
-        <v>1140.245251388622</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="F10" t="n">
-        <v>1264.606223980558</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="G10" t="n">
-        <v>1264.606223980558</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="H10" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="I10" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="J10" t="n">
-        <v>1434.122809139956</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="K10" t="n">
         <v>1544.487243076824</v>
@@ -4986,19 +4986,19 @@
         <v>259.005934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>259.005934252978</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>408.8977678642555</v>
+        <v>704.3785197772106</v>
       </c>
       <c r="W10" t="n">
-        <v>408.8977678642555</v>
+        <v>876.269438036888</v>
       </c>
       <c r="X10" t="n">
-        <v>559.9285588884489</v>
+        <v>1027.300229061082</v>
       </c>
       <c r="Y10" t="n">
-        <v>671.3378595674812</v>
+        <v>1138.709529740114</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I11" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>576.7999999999998</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>1131.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1797.400904947332</v>
+        <v>1685.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q11" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R11" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I12" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J12" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K12" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L12" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M12" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N12" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O12" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P12" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W12" t="n">
-        <v>564.8317184882503</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X12" t="n">
-        <v>494.2632948060407</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C13" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D13" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E13" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F13" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G13" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H13" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I13" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J13" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K13" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L13" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M13" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N13" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O13" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P13" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q13" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R13" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S13" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U13" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V13" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W13" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X13" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y13" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I14" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="K14" t="n">
-        <v>598.13</v>
+        <v>620.3511712710648</v>
       </c>
       <c r="L14" t="n">
-        <v>1151.54</v>
+        <v>620.3511712710648</v>
       </c>
       <c r="M14" t="n">
-        <v>1662.388828728935</v>
+        <v>1131.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2215.798828728935</v>
+        <v>1685.6</v>
       </c>
       <c r="O14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="P14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="Q14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R14" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S14" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D15" t="n">
-        <v>110.1140157855959</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E15" t="n">
-        <v>110.1140157855959</v>
+        <v>387.8669114524009</v>
       </c>
       <c r="F15" t="n">
-        <v>110.1140157855959</v>
+        <v>44.8</v>
       </c>
       <c r="G15" t="n">
-        <v>110.1140157855959</v>
+        <v>44.8</v>
       </c>
       <c r="H15" t="n">
-        <v>110.1140157855959</v>
+        <v>44.8</v>
       </c>
       <c r="I15" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J15" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M15" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N15" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O15" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1192.195551353737</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C16" t="n">
-        <v>1268.697557172173</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D16" t="n">
-        <v>1332.516701297173</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E16" t="n">
-        <v>1400.845605508586</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F16" t="n">
-        <v>1475.706578100521</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G16" t="n">
-        <v>1579.613143987407</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H16" t="n">
-        <v>1699.629729146804</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I16" t="n">
-        <v>1871.262608082887</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J16" t="n">
-        <v>2182.846348735339</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K16" t="n">
-        <v>2236</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L16" t="n">
-        <v>2161.709466507294</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M16" t="n">
-        <v>1989.354303474415</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N16" t="n">
-        <v>1765.935035523218</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O16" t="n">
-        <v>1472.555677867648</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P16" t="n">
-        <v>1131.699215919893</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q16" t="n">
-        <v>752.0635932677734</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R16" t="n">
-        <v>371.6574033878228</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S16" t="n">
-        <v>359.1589390415042</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>497.7346182003091</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U16" t="n">
-        <v>694.7858108385957</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V16" t="n">
-        <v>844.1072037245417</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W16" t="n">
-        <v>966.4981219842191</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X16" t="n">
-        <v>1068.028913008413</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y16" t="n">
-        <v>1129.938213687445</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C17" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D17" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E17" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I17" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>598.13</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1151.54</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1662.388828728935</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N17" t="n">
-        <v>2215.798828728935</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>2215.798828728935</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>2215.798828728935</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q17" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R17" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X17" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y17" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.9618669904511</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C18" t="n">
-        <v>373.7498342171993</v>
+        <v>44.8</v>
       </c>
       <c r="D18" t="n">
-        <v>373.7498342171993</v>
+        <v>44.8</v>
       </c>
       <c r="E18" t="n">
-        <v>373.7498342171993</v>
+        <v>44.8</v>
       </c>
       <c r="F18" t="n">
-        <v>373.7498342171993</v>
+        <v>44.8</v>
       </c>
       <c r="G18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I18" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J18" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M18" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N18" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V18" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8924310491303</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>274.6872361907176</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H19" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I19" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J19" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K19" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L19" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M19" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N19" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O19" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P19" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q19" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R19" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S19" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I20" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J20" t="n">
-        <v>44.72</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="K20" t="n">
-        <v>598.13</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="L20" t="n">
-        <v>1151.54</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="M20" t="n">
-        <v>1662.388828728935</v>
+        <v>576.7999999999998</v>
       </c>
       <c r="N20" t="n">
-        <v>2215.798828728935</v>
+        <v>1131.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2215.798828728935</v>
+        <v>1685.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2215.798828728935</v>
+        <v>2240</v>
       </c>
       <c r="Q20" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R20" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S20" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>119.2429040110725</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0308712378207</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D21" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E21" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="F21" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="G21" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="H21" t="n">
-        <v>44.72</v>
+        <v>264.1195817084329</v>
       </c>
       <c r="I21" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J21" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N21" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O21" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X21" t="n">
-        <v>204.0388125085078</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y21" t="n">
-        <v>154.1485167851398</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C22" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D22" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E22" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F22" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G22" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H22" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I22" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J22" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K22" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L22" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M22" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N22" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O22" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P22" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q22" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R22" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S22" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T22" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U22" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V22" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W22" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X22" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y22" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4004881699675</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H23" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I23" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>598.13</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>598.13</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>1108.978828728935</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="N23" t="n">
-        <v>1662.388828728935</v>
+        <v>990.5091130376557</v>
       </c>
       <c r="O23" t="n">
-        <v>2215.798828728935</v>
+        <v>1544.909113037656</v>
       </c>
       <c r="P23" t="n">
-        <v>2215.798828728935</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q23" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S23" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>472.8582575464263</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="D24" t="n">
-        <v>461.5662247731743</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="E24" t="n">
-        <v>115.4327932358888</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>461.6462247731745</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>380.3233203903244</v>
       </c>
       <c r="H24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I24" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J24" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N24" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O24" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>507.7638703204935</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>870.0458296400257</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D25" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H25" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I25" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J25" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K25" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L25" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M25" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N25" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O25" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P25" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q25" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R25" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S25" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W25" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X25" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y25" t="n">
-        <v>807.7884919737335</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C26" t="n">
-        <v>332.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D26" t="n">
-        <v>271.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E26" t="n">
-        <v>217.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F26" t="n">
-        <v>161.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G26" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I26" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J26" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K26" t="n">
-        <v>598.13</v>
+        <v>599.2</v>
       </c>
       <c r="L26" t="n">
-        <v>733.1420762183976</v>
+        <v>599.2</v>
       </c>
       <c r="M26" t="n">
-        <v>1243.990904947333</v>
+        <v>1110.048828728935</v>
       </c>
       <c r="N26" t="n">
-        <v>1797.400904947332</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q26" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R26" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S26" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T26" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U26" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V26" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W26" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X26" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y26" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I27" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J27" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L27" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M27" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N27" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O27" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>1136.841549130715</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>819.8336731135525</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T27" t="n">
-        <v>763.9167385504073</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U27" t="n">
-        <v>713.1992034391076</v>
+        <v>423.0547211415749</v>
       </c>
       <c r="V27" t="n">
-        <v>294.5015598113094</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W27" t="n">
-        <v>211.2963649528968</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X27" t="n">
-        <v>140.7279412706871</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C28" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D28" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E28" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F28" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G28" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H28" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I28" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J28" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K28" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L28" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M28" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N28" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O28" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P28" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q28" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R28" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S28" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T28" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U28" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V28" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W28" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X28" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y28" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>217.0655061454243</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I29" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J29" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M29" t="n">
-        <v>946.8779417665908</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N29" t="n">
-        <v>1129.18</v>
+        <v>1131.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1682.59</v>
+        <v>1685.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="Q29" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R29" t="n">
-        <v>2236</v>
+        <v>2232.074554156147</v>
       </c>
       <c r="S29" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.76327354774</v>
       </c>
       <c r="T29" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.697029377473</v>
       </c>
       <c r="U29" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V29" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W29" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X29" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y29" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>275.2516144816847</v>
+        <v>385.0418669904512</v>
       </c>
       <c r="C30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="D30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="E30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="F30" t="n">
-        <v>264.0395817084329</v>
+        <v>373.8298342171994</v>
       </c>
       <c r="G30" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="H30" t="n">
-        <v>264.0395817084329</v>
+        <v>44.8</v>
       </c>
       <c r="I30" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J30" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L30" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M30" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N30" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O30" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P30" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S30" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T30" t="n">
-        <v>827.2276097882281</v>
+        <v>739.4912192322532</v>
       </c>
       <c r="U30" t="n">
-        <v>776.5100746769283</v>
+        <v>688.7736841209535</v>
       </c>
       <c r="V30" t="n">
-        <v>711.3477845844836</v>
+        <v>623.6113940285088</v>
       </c>
       <c r="W30" t="n">
-        <v>628.142589726071</v>
+        <v>540.4061991700961</v>
       </c>
       <c r="X30" t="n">
-        <v>557.5741660438614</v>
+        <v>469.8377754878865</v>
       </c>
       <c r="Y30" t="n">
-        <v>310.1572272557519</v>
+        <v>419.9474797645184</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C31" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D31" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E31" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F31" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G31" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H31" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I31" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J31" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K31" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L31" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M31" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N31" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O31" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P31" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q31" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R31" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S31" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T31" t="n">
-        <v>175.5848964865977</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U31" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V31" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W31" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X31" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y31" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C32" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H32" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I32" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>598.13</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>598.13</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1108.978828728935</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N32" t="n">
-        <v>1108.978828728935</v>
+        <v>1501.357941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1243.990904947333</v>
+        <v>1685.6</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2240</v>
       </c>
       <c r="Q32" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R32" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S32" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T32" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U32" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I33" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J33" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L33" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N33" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O33" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>937.5750872192207</v>
+        <v>647.4306049216879</v>
       </c>
       <c r="S33" t="n">
-        <v>819.8336731135527</v>
+        <v>466.3783195781991</v>
       </c>
       <c r="T33" t="n">
-        <v>410.3813850150538</v>
+        <v>410.4613850150538</v>
       </c>
       <c r="U33" t="n">
-        <v>359.6638499037541</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V33" t="n">
-        <v>294.5015598113094</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W33" t="n">
-        <v>211.2963649528968</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X33" t="n">
-        <v>140.7279412706871</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y33" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>870.0458296400257</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C34" t="n">
-        <v>946.5478354584615</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F34" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G34" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H34" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I34" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J34" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K34" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L34" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M34" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N34" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O34" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P34" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R34" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S34" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>372.6360891248843</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V34" t="n">
-        <v>521.9574820108303</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W34" t="n">
-        <v>644.3484002705077</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X34" t="n">
-        <v>745.8791912947012</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y34" t="n">
-        <v>807.7884919737335</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.8</v>
       </c>
       <c r="I35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="L35" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="M35" t="n">
-        <v>555.568828728935</v>
+        <v>555.648828728935</v>
       </c>
       <c r="N35" t="n">
-        <v>1108.978828728935</v>
+        <v>1110.048828728935</v>
       </c>
       <c r="O35" t="n">
-        <v>1662.388828728935</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2215.798828728935</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q35" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="D36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="E36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="F36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="G36" t="n">
-        <v>461.5662247731743</v>
+        <v>44.8</v>
       </c>
       <c r="H36" t="n">
-        <v>126.0429043828499</v>
+        <v>44.8</v>
       </c>
       <c r="I36" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J36" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K36" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L36" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M36" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N36" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O36" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>274.6872361907176</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>204.1188125085079</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J37" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K37" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L37" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M37" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N37" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O37" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P37" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R37" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S37" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.6648964865979</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4804881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>329.0011162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>268.052474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>213.1400603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>157.695990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>103.3956148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I38" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130376558</v>
+        <v>436.1091130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>1500.287941766591</v>
+        <v>946.9579417665907</v>
       </c>
       <c r="N38" t="n">
-        <v>1797.400904947332</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>1247.000904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.453295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.775493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4891539265824</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.7600292188372</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.8131275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>391.5353531635762</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>380.3233203903244</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>380.3233203903244</v>
       </c>
       <c r="E39" t="n">
-        <v>461.5662247731743</v>
+        <v>380.3233203903244</v>
       </c>
       <c r="F39" t="n">
-        <v>373.7498342171993</v>
+        <v>380.3233203903244</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>380.3233203903244</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I39" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J39" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K39" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L39" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N39" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O39" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P39" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>919.6430540741914</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>801.9016399685233</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>745.9847054053781</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>695.2671702940784</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>630.1048802016337</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>546.8996853432211</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>476.3312616610115</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>426.4409659376435</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I40" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J40" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K40" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L40" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M40" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N40" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O40" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P40" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R40" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S40" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T40" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C41" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D41" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F41" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G41" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H41" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J41" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="K41" t="n">
-        <v>598.13</v>
+        <v>599.2</v>
       </c>
       <c r="L41" t="n">
-        <v>598.13</v>
+        <v>599.2</v>
       </c>
       <c r="M41" t="n">
-        <v>1108.978828728935</v>
+        <v>1110.048828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>1664.448828728935</v>
       </c>
       <c r="O41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>1801.400904947332</v>
       </c>
       <c r="Q41" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R41" t="n">
-        <v>2231.994554156147</v>
+        <v>2240</v>
       </c>
       <c r="S41" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U41" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V41" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W41" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X41" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y41" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I42" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J42" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K42" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M42" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N42" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O42" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T42" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9967385504074</v>
       </c>
       <c r="U42" t="n">
-        <v>422.9747211415747</v>
+        <v>359.743849903754</v>
       </c>
       <c r="V42" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5815598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>274.6072361907175</v>
+        <v>211.3763649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>140.8079412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>90.9176455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>870.1258296400258</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>946.6278354584616</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1010.446979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1078.775883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1153.63685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1257.543422273696</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1377.560007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1549.192886369176</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021627</v>
+        <v>1860.776627021628</v>
       </c>
       <c r="K43" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L43" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M43" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N43" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O43" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P43" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q43" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R43" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S43" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>372.7160891248845</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>522.0374820108304</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>644.4284002705078</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>745.9591912947013</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>807.8684919737336</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>437.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>336.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>275.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>221.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>165.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>111.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>52.72544584385304</v>
       </c>
       <c r="I44" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>65.95117127106482</v>
       </c>
       <c r="L44" t="n">
-        <v>1129.18</v>
+        <v>620.3511712710648</v>
       </c>
       <c r="M44" t="n">
-        <v>1129.18</v>
+        <v>1131.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1129.18</v>
+        <v>1685.6</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>2240</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="Q44" t="n">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="R44" t="n">
-        <v>2231.994554156147</v>
+        <v>2240</v>
       </c>
       <c r="S44" t="n">
-        <v>2085.68327354774</v>
+        <v>2093.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1854.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1552.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1269.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>978.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>733.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>570.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>56.01203277325182</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="I45" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="J45" t="n">
-        <v>168.6765201752989</v>
+        <v>168.756520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>357.8693362696823</v>
+        <v>357.9493362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>629.2197978648824</v>
+        <v>629.2997978648825</v>
       </c>
       <c r="M45" t="n">
-        <v>715.3003396077416</v>
+        <v>715.3803396077418</v>
       </c>
       <c r="N45" t="n">
-        <v>848.58062421531</v>
+        <v>848.6606242153101</v>
       </c>
       <c r="O45" t="n">
-        <v>1087.623075899029</v>
+        <v>1087.703075899029</v>
       </c>
       <c r="P45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.152420368536</v>
+        <v>1200.232420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>1000.965958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>883.2245443513734</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>827.3076097882282</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>776.5900746769285</v>
       </c>
       <c r="V45" t="n">
-        <v>648.0369133466629</v>
+        <v>711.4277845844838</v>
       </c>
       <c r="W45" t="n">
-        <v>564.8317184882503</v>
+        <v>628.2225897260712</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>557.6541660438616</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>444.4529990826726</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>877.7566123122328</v>
+        <v>877.8366123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>954.2586181306687</v>
+        <v>954.3386181306686</v>
       </c>
       <c r="D46" t="n">
-        <v>1018.077762255669</v>
+        <v>1018.157762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1086.406666467082</v>
+        <v>1086.486666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1161.267639059017</v>
+        <v>1161.347639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1265.174204945903</v>
+        <v>1265.254204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.2707901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.903669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.487409693834</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958496</v>
+        <v>1921.641060958496</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465789</v>
+        <v>1847.35052746579</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432911</v>
+        <v>1674.995364432911</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.496096481714</v>
+        <v>1451.576096481714</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826143</v>
+        <v>1158.196738826143</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783884</v>
+        <v>817.3402768783884</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262692</v>
+        <v>437.7046542262692</v>
       </c>
       <c r="R46" t="n">
-        <v>57.21846434631862</v>
+        <v>57.29846434631862</v>
       </c>
       <c r="S46" t="n">
-        <v>44.72</v>
+        <v>44.8</v>
       </c>
       <c r="T46" t="n">
-        <v>183.2956791588049</v>
+        <v>183.3756791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>380.3468717970915</v>
+        <v>380.4268717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>529.6682646830375</v>
+        <v>529.7482646830374</v>
       </c>
       <c r="W46" t="n">
-        <v>652.0591829427149</v>
+        <v>652.1391829427148</v>
       </c>
       <c r="X46" t="n">
-        <v>753.5899739669084</v>
+        <v>753.6699739669083</v>
       </c>
       <c r="Y46" t="n">
-        <v>815.4992746459407</v>
+        <v>815.5792746459406</v>
       </c>
     </row>
   </sheetData>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>965.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>474.2377685639915</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>78.97603822292498</v>
+        <v>474.2377685639915</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
@@ -8684,19 +8684,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>686.3741346749881</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>370.3619737970638</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,22 +8912,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>56.40782571081238</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O14" t="n">
-        <v>90.65309308021877</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>373.3215697566601</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>56.40782571081238</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>193.2279078336117</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>259.3696781312642</v>
       </c>
       <c r="Q23" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,19 +9863,19 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L26" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1036.248958069835</v>
+        <v>615.584388593469</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
@@ -10109,13 +10109,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>661.3924512348954</v>
+        <v>663.352047194491</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>559.2870600406815</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q29" t="n">
         <v>172.8226843274854</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10346,16 +10346,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>206.6237041381304</v>
+        <v>256.3509586987484</v>
       </c>
       <c r="P32" t="n">
-        <v>559.2870600406815</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10583,16 +10583,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>208.5833000977262</v>
       </c>
       <c r="P35" t="n">
-        <v>559.2870600406815</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10814,19 +10814,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>777.3630622928066</v>
+        <v>780.3226582524026</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>560.2870600406815</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,7 +11048,7 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>613.6247926338732</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>208.5833000977262</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>56.40782571081238</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>141.1524110730752</v>
+        <v>560</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1037.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>630.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3337784.501605552</v>
+        <v>3337831.779181309</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4156379.577821739</v>
+        <v>4156426.855397496</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4974974.654037924</v>
+        <v>4975021.931613683</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5793569.730254108</v>
+        <v>5793617.007829866</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6612164.806470292</v>
+        <v>6612212.08404605</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7430759.882686475</v>
+        <v>7430807.160262234</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8249354.958902658</v>
+        <v>8249402.236478416</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9067950.035118848</v>
+        <v>9067997.312694605</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9886545.111335039</v>
+        <v>9886592.388910796</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10705140.18755123</v>
+        <v>10705187.46512699</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11523735.26376742</v>
+        <v>11523782.54134318</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12342330.33998362</v>
+        <v>12342377.61755937</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365853</v>
       </c>
       <c r="C2" t="n">
         <v>1385314.744365854</v>
       </c>
       <c r="D2" t="n">
-        <v>1385314.744365853</v>
+        <v>1385314.744365854</v>
       </c>
       <c r="E2" t="n">
         <v>1385314.744365854</v>
@@ -26290,19 +26290,19 @@
         <v>1385314.744365854</v>
       </c>
       <c r="I2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365853</v>
       </c>
       <c r="J2" t="n">
-        <v>1385314.744365854</v>
+        <v>1385314.744365853</v>
       </c>
       <c r="K2" t="n">
         <v>1385314.744365854</v>
       </c>
       <c r="L2" t="n">
+        <v>1385314.744365855</v>
+      </c>
+      <c r="M2" t="n">
         <v>1385314.744365854</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1385314.744365853</v>
       </c>
       <c r="N2" t="n">
         <v>1385314.744365854</v>
@@ -26311,7 +26311,7 @@
         <v>1385314.744365854</v>
       </c>
       <c r="P2" t="n">
-        <v>1385314.744365853</v>
+        <v>1385314.744365854</v>
       </c>
     </row>
     <row r="3">
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>328576</v>
+        <v>328928</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>48576</v>
+        <v>48928</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724099</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743712</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544712.0690347301</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542769.886429081</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540825.0236843044</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538877.4615810197</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>536927.1806494283</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>534974.1611645631</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533018.3831414287</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531059.8263300108</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529098.4702101597</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527134.2939863529</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525167.2765823142</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523197.3966354961</v>
       </c>
     </row>
     <row r="5">
@@ -26434,40 +26434,40 @@
         <v>59224.39999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="F5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="G5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="H5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="I5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="J5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="K5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="L5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="M5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="N5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="O5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35</v>
+        <v>63472.15</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>611543.3851233445</v>
+        <v>609980.7720298987</v>
       </c>
       <c r="C6" t="n">
-        <v>761767.9008868892</v>
+        <v>760205.2877934438</v>
       </c>
       <c r="D6" t="n">
-        <v>763803.1738849274</v>
+        <v>762240.5607914825</v>
       </c>
       <c r="E6" t="n">
-        <v>450233.3411393185</v>
+        <v>448202.5253311236</v>
       </c>
       <c r="F6" t="n">
-        <v>780752.2364848227</v>
+        <v>779072.707936773</v>
       </c>
       <c r="G6" t="n">
-        <v>782697.8129530085</v>
+        <v>781017.5706815497</v>
       </c>
       <c r="H6" t="n">
-        <v>784646.0897703097</v>
+        <v>782965.1327848345</v>
       </c>
       <c r="I6" t="n">
-        <v>786597.0864136697</v>
+        <v>784915.4137164252</v>
       </c>
       <c r="J6" t="n">
-        <v>360358.8226152948</v>
+        <v>358676.4332012903</v>
       </c>
       <c r="K6" t="n">
-        <v>790507.3183675145</v>
+        <v>788824.2112244257</v>
       </c>
       <c r="L6" t="n">
-        <v>792466.5939277735</v>
+        <v>790782.7680358439</v>
       </c>
       <c r="M6" t="n">
-        <v>745852.6698237528</v>
+        <v>743816.124155694</v>
       </c>
       <c r="N6" t="n">
-        <v>796393.5668586064</v>
+        <v>794708.3003795011</v>
       </c>
       <c r="O6" t="n">
-        <v>518361.306116345</v>
+        <v>516675.3177835398</v>
       </c>
       <c r="P6" t="n">
-        <v>800331.9089673545</v>
+        <v>798645.1977303579</v>
       </c>
     </row>
   </sheetData>
@@ -26868,40 +26868,40 @@
         <v>421</v>
       </c>
       <c r="E4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="I4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="J4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P4" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -26972,28 +26972,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>350</v>
@@ -27002,19 +27002,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27024,13 +27024,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -27042,31 +27042,31 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -27079,46 +27079,46 @@
         <v>421</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>231.5850086145854</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>190.3876496598538</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>232.275552502327</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27597,16 +27597,16 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
+        <v>398.3756069790886</v>
+      </c>
+      <c r="F4" t="n">
         <v>400</v>
       </c>
-      <c r="E4" t="n">
-        <v>280.9809048369565</v>
-      </c>
-      <c r="F4" t="n">
-        <v>274.3828559677419</v>
-      </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>355.966375367988</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,10 +27645,10 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27758,16 +27758,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27803,13 +27803,13 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
+        <v>224.5827151763668</v>
+      </c>
+      <c r="U6" t="n">
         <v>400</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
       <c r="V6" t="n">
-        <v>274.4424628029984</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27837,16 +27837,16 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>336.2326479955244</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
         <v>176.6334556201183</v>
@@ -27855,7 +27855,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27891,13 +27891,13 @@
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>353.6348559539881</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>82.46360744287983</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>274.1600119267409</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,10 +28040,10 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>115.3536407070567</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28074,16 +28074,16 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>336.2326479955244</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
         <v>176.6334556201183</v>
@@ -28092,7 +28092,7 @@
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,13 +28122,13 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>350.5762027528601</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28232,10 +28232,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343468</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
@@ -28286,13 +28286,13 @@
         <v>350</v>
       </c>
       <c r="W12" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X12" t="n">
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -28356,13 +28356,13 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
       </c>
       <c r="V13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W13" t="n">
         <v>350</v>
@@ -28387,7 +28387,7 @@
         <v>350</v>
       </c>
       <c r="D14" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="E14" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28466,13 +28466,13 @@
         <v>350</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>269.6305770343468</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28481,7 +28481,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>152.3863102636086</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28566,7 +28566,7 @@
         <v>350</v>
       </c>
       <c r="K16" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L16" t="n">
         <v>350</v>
@@ -28593,7 +28593,7 @@
         <v>350</v>
       </c>
       <c r="T16" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U16" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28678,7 +28678,7 @@
         <v>350</v>
       </c>
       <c r="V17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W17" t="n">
         <v>350</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>263.0617733495848</v>
+        <v>350</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28712,7 +28712,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H18" t="n">
         <v>332.1680871864211</v>
@@ -28757,13 +28757,13 @@
         <v>350</v>
       </c>
       <c r="V18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>350</v>
       </c>
       <c r="X18" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="Y18" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28842,7 +28842,7 @@
         <v>350</v>
       </c>
       <c r="X19" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="Y19" t="n">
         <v>350</v>
@@ -28873,7 +28873,7 @@
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28912,7 +28912,7 @@
         <v>350</v>
       </c>
       <c r="U20" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V20" t="n">
         <v>350</v>
@@ -28940,7 +28940,7 @@
         <v>350</v>
       </c>
       <c r="D21" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>342.6720972219126</v>
@@ -28952,10 +28952,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523269</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -29000,7 +29000,7 @@
         <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y21" t="n">
         <v>350</v>
@@ -29067,7 +29067,7 @@
         <v>350</v>
       </c>
       <c r="T22" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U22" t="n">
         <v>350</v>
@@ -29082,7 +29082,7 @@
         <v>350</v>
       </c>
       <c r="Y22" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23">
@@ -29143,7 +29143,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T23" t="n">
         <v>350</v>
@@ -29161,7 +29161,7 @@
         <v>350</v>
       </c>
       <c r="Y23" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
     </row>
     <row r="24">
@@ -29180,16 +29180,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>269.6305770343469</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360058</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29253,7 +29253,7 @@
         <v>350</v>
       </c>
       <c r="C25" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="D25" t="n">
         <v>350</v>
@@ -29313,7 +29313,7 @@
         <v>350</v>
       </c>
       <c r="W25" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="X25" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>110.4015025650371</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
         <v>350</v>
@@ -29465,10 +29465,10 @@
         <v>350</v>
       </c>
       <c r="U27" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="W27" t="n">
         <v>350</v>
@@ -29541,7 +29541,7 @@
         <v>350</v>
       </c>
       <c r="T28" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29581,7 +29581,7 @@
         <v>350</v>
       </c>
       <c r="G29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H29" t="n">
         <v>350</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>243.0324074428798</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29660,13 +29660,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29699,7 +29699,7 @@
         <v>350</v>
       </c>
       <c r="T30" t="n">
-        <v>350</v>
+        <v>263.0617733495848</v>
       </c>
       <c r="U30" t="n">
         <v>350</v>
@@ -29714,7 +29714,7 @@
         <v>350</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31">
@@ -29778,7 +29778,7 @@
         <v>350</v>
       </c>
       <c r="T31" t="n">
-        <v>342.2113306341342</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U31" t="n">
         <v>350</v>
@@ -29818,13 +29818,13 @@
         <v>350</v>
       </c>
       <c r="G32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H32" t="n">
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29930,13 +29930,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>287.3222374745576</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U33" t="n">
         <v>350</v>
@@ -29967,7 +29967,7 @@
         <v>350</v>
       </c>
       <c r="D34" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="E34" t="n">
         <v>350</v>
@@ -30015,7 +30015,7 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
@@ -30055,13 +30055,13 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30137,10 +30137,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>136.6167105523271</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30182,13 +30182,13 @@
         <v>350</v>
       </c>
       <c r="W36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>350</v>
       </c>
       <c r="Y36" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
     </row>
     <row r="37">
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30280,7 +30280,7 @@
         <v>350</v>
       </c>
       <c r="C38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="D38" t="n">
         <v>350</v>
@@ -30334,7 +30334,7 @@
         <v>350</v>
       </c>
       <c r="U38" t="n">
-        <v>350</v>
+        <v>342.1538086145855</v>
       </c>
       <c r="V38" t="n">
         <v>350</v>
@@ -30368,13 +30368,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>252.6980156874616</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>217.1263858913485</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>350</v>
+        <v>269.4903246609784</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30453,10 +30453,10 @@
         <v>350</v>
       </c>
       <c r="H40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I40" t="n">
-        <v>350</v>
+        <v>342.2113306341345</v>
       </c>
       <c r="J40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30647,7 +30647,7 @@
         <v>350</v>
       </c>
       <c r="T42" t="n">
-        <v>350</v>
+        <v>287.3222374745574</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>350</v>
       </c>
       <c r="X42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30726,10 +30726,10 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="V43" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>142.2349682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>350</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30890,16 +30890,16 @@
         <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>287.3222374745573</v>
       </c>
     </row>
     <row r="46">
@@ -30927,7 +30927,7 @@
         <v>350</v>
       </c>
       <c r="H46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I46" t="n">
         <v>350</v>
@@ -30936,7 +30936,7 @@
         <v>350</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>342.2113306341344</v>
       </c>
       <c r="L46" t="n">
         <v>350</v>
@@ -34752,10 +34752,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>421</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>403.989898989899</v>
@@ -34883,16 +34883,16 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>117.394702142132</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>320.6974265320802</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34931,10 +34931,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -35123,16 +35123,16 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>55.25174315856783</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,7 +35168,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35177,13 +35177,13 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>127.2620461152784</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35232,7 +35232,7 @@
         <v>421</v>
       </c>
       <c r="O8" t="n">
-        <v>8.728168648832536</v>
+        <v>403.989898989899</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35360,16 +35360,16 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>55.25174315856783</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -35378,7 +35378,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,13 +35408,13 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>151.4058925366439</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35463,19 +35463,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>142.1120070326708</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O11" t="n">
-        <v>300.1141042229714</v>
+        <v>560</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q11" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35642,13 +35642,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W13" t="n">
         <v>123.6271901612903</v>
@@ -35691,22 +35691,22 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L14" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O14" t="n">
-        <v>20.40522350612631</v>
+        <v>560</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K16" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,7 +35879,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U16" t="n">
         <v>199.0416087255421</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>303.0737001825676</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36128,7 +36128,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X19" t="n">
-        <v>102.5563545698924</v>
+        <v>94.7676852040268</v>
       </c>
       <c r="Y19" t="n">
         <v>62.53464715053764</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U22" t="n">
         <v>199.0416087255421</v>
@@ -36368,7 +36368,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y22" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="23">
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O23" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>259.0826180905828</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36539,7 +36539,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608974</v>
       </c>
       <c r="D25" t="n">
         <v>64.46378194444452</v>
@@ -36599,7 +36599,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W25" t="n">
-        <v>115.8385207954244</v>
+        <v>123.6271901612903</v>
       </c>
       <c r="X25" t="n">
         <v>102.5563545698924</v>
@@ -36642,19 +36642,19 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L26" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>559</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36888,13 +36888,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>184.1434931650601</v>
+        <v>186.1030891246557</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P29" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>132.1867641278765</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U31" t="n">
         <v>199.0416087255421</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37125,16 +37125,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O32" t="n">
-        <v>136.375834564038</v>
+        <v>186.1030891246559</v>
       </c>
       <c r="P32" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37253,7 +37253,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D34" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857893</v>
       </c>
       <c r="E34" t="n">
         <v>69.01909516304346</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
@@ -37362,16 +37362,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="P35" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q35" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278766</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37593,19 +37593,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>300.1141042229714</v>
+        <v>303.0737001825674</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37739,10 +37739,10 @@
         <v>104.95612715847</v>
       </c>
       <c r="H40" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I40" t="n">
-        <v>173.3665443798817</v>
+        <v>165.5778750140162</v>
       </c>
       <c r="J40" t="n">
         <v>314.7310511640923</v>
@@ -37827,7 +37827,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37836,10 +37836,10 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>136.375834564038</v>
+        <v>560</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>138.3354305236338</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596764</v>
       </c>
       <c r="V43" t="n">
         <v>150.8296897837838</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>21.36481946572204</v>
       </c>
       <c r="K44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>141.1524110730752</v>
+        <v>560</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>560</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H46" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I46" t="n">
         <v>173.3665443798817</v>
@@ -38222,7 +38222,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299136</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
